--- a/product_selector_out/STM32F102.xlsx
+++ b/product_selector_out/STM32F102.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM19"/>
+  <dimension ref="A1:BN19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.39453125" customWidth="1" min="1" max="1"/>
@@ -561,7 +561,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -889,6 +890,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -984,6 +990,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1308,6 +1315,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f102c8.pdf</t>
         </is>
       </c>
@@ -1635,6 +1647,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f102c4.pdf</t>
         </is>
       </c>
@@ -1962,6 +1979,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f102c4.pdf</t>
         </is>
       </c>
@@ -2289,6 +2311,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f102c8.pdf</t>
         </is>
       </c>
@@ -2616,6 +2643,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f102c8.pdf</t>
         </is>
       </c>
@@ -2943,6 +2975,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f102c4.pdf</t>
         </is>
       </c>
@@ -3270,6 +3307,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f102c4.pdf</t>
         </is>
       </c>
@@ -3597,12 +3639,17 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f102c8.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -3623,16 +3670,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -3645,6 +3690,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -3664,7 +3710,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -3689,7 +3737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM19"/>
+  <dimension ref="A1:BN19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3757,6 +3805,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4090,6 +4139,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -4185,6 +4239,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -4507,7 +4562,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -4834,7 +4894,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5161,7 +5226,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5488,7 +5558,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5815,7 +5890,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6142,7 +6222,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6469,7 +6554,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6796,7 +6886,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6804,8 +6899,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
